--- a/Data/MAP Stages- Inputs_Outputs.xlsx
+++ b/Data/MAP Stages- Inputs_Outputs.xlsx
@@ -3,9 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="24735" windowHeight="17715" tabRatio="500" activeTab="2"/>
+    <workbookView windowWidth="30240" windowHeight="13840" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Process Diagram" sheetId="1" r:id="rId1"/>
@@ -14,12 +13,25 @@
     <sheet name="Organigram" sheetId="4" r:id="rId4"/>
     <sheet name="Glossary_Lifecycle" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="348">
   <si>
     <t>N°</t>
   </si>
@@ -96,29 +108,124 @@
     <t>Estimate Project Size, Impact and Strategic Fit</t>
   </si>
   <si>
-    <t>*Mission Statement
+    <r>
+      <t>*Mission Statement
 *Business Goals
 *Customer Goals
-*Business Objectives
-*Business Goals</t>
+*Business Objectives</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Business Goals</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customer Objectives</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>= Mission One Pager</t>
+    </r>
   </si>
   <si>
     <t>Project Estimation</t>
   </si>
   <si>
     <t>Define High Level Risks</t>
+  </si>
+  <si>
+    <t>Mission One Pager
+Project Estimation</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List of Major Risks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>=Project Charter</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate resources to MAP project </t>
   </si>
   <si>
     <t>Mision One Pager
 Project Estimation</t>
   </si>
   <si>
-    <t>List of Major Risks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate resources to MAP project </t>
-  </si>
-  <si>
     <t>*type of ressources
 *ressources usage</t>
   </si>
@@ -126,7 +233,18 @@
     <t>Allocate team members for MAP project</t>
   </si>
   <si>
-    <t>Ressources allocation</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Ressources allocation</t>
+    </r>
   </si>
   <si>
     <t>Head of assigned ressources</t>
@@ -135,26 +253,128 @@
     <t>Estimate MAP Project Duration</t>
   </si>
   <si>
-    <t>*Mision One Pager
-*Project Estimation
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mision One Pager
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Project Estimation
 *ressources allocation</t>
-  </si>
-  <si>
-    <t>MAP lead time</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MAP lead time </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>= MAP Duration</t>
+    </r>
   </si>
   <si>
     <t>ONE PAGER TEMPLATE COMPLETED</t>
   </si>
   <si>
-    <t>*Problem Statement
-*Mission Statement
+    <r>
+      <t xml:space="preserve">*Problem Statement </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(Problem Canvas)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Mission Statement
 *Business Goals
 *Customer Goals
 *Business Objectives
 *Customer Objectives
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= Mission One Pager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
 *Project Size 
 *Impact 
-*Startegic Fit</t>
+*Strategic Fit</t>
+    </r>
   </si>
   <si>
     <t>One Pager Template</t>
@@ -166,17 +386,87 @@
     <t>Elaborate MAP Project Charter</t>
   </si>
   <si>
-    <t>*Mission Statement
+    <r>
+      <t>*Mission Statement
 *Business Goals
 *Customer Goals
 *Business Objectives
-*Customer Objectives
-*List of Major Risks
+*Customer Objectives</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Mission One Pager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+*List of Major Risks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> =Project Charter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
 *ressources allocation
-*MAP lead time</t>
-  </si>
-  <si>
-    <t>MAP Project Charter template</t>
+*MAP lead time </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>= MAP Duration</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MAP Project Charter </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>template</t>
+    </r>
   </si>
   <si>
     <t>Rate MAP project (Stage 1)</t>
@@ -186,7 +476,18 @@
 MAP Project Charter</t>
   </si>
   <si>
-    <t>MAP project rating</t>
+    <r>
+      <t xml:space="preserve">MAP project rating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>gate 1</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">VP Zumtobel Brand &amp; Application
@@ -196,6 +497,20 @@
   </si>
   <si>
     <t>Gate 1 decision</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MAP project rating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>gate1</t>
+    </r>
   </si>
   <si>
     <t>Approval for moving to Stage 2
@@ -309,7 +624,35 @@
 *Risk Identification</t>
   </si>
   <si>
+    <t>MAP project rating</t>
+  </si>
+  <si>
     <t>Gate 2 decision</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Approval for moving to Stage </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+OR
+Rejection</t>
+    </r>
   </si>
   <si>
     <t>Field ID</t>
@@ -543,6 +886,9 @@
     <t>Project Charter</t>
   </si>
   <si>
+    <t>List of Major Risks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Formulate factors that potentially negatively impact the undertaking. Consider factors such as market situation, development efforts / system complexity, available internal knowledge, organization maturity, legal and regulatory situation  </t>
   </si>
   <si>
@@ -574,6 +920,9 @@
   </si>
   <si>
     <t>MAP Duration</t>
+  </si>
+  <si>
+    <t>MAP lead time</t>
   </si>
   <si>
     <t>Estimate the lead time of the MAP project</t>
@@ -1187,14 +1536,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1234,10 +1583,44 @@
       <charset val="1"/>
     </font>
     <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1246,11 +1629,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1262,21 +1640,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1290,6 +1661,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -1298,18 +1677,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1330,42 +1702,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -1381,9 +1724,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1393,6 +1757,48 @@
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1429,7 +1835,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1441,85 +1907,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1537,19 +1949,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1573,7 +1973,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1585,19 +1985,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1609,7 +2003,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1658,11 +2064,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1682,46 +2112,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1741,159 +2142,164 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1919,58 +2325,71 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
     <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2071,8 +2490,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="661670" y="190500"/>
-          <a:ext cx="34852610" cy="7771765"/>
+          <a:off x="705485" y="213360"/>
+          <a:ext cx="37130990" cy="8686165"/>
           <a:chOff x="611640" y="181080"/>
           <a:chExt cx="32244480" cy="7391160"/>
         </a:xfrm>
@@ -2184,8 +2603,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1323340" y="9144000"/>
-          <a:ext cx="27378660" cy="5885815"/>
+          <a:off x="1410970" y="10241280"/>
+          <a:ext cx="29175075" cy="6571615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2230,7 +2649,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="95250" y="38100"/>
-          <a:ext cx="18653125" cy="7314565"/>
+          <a:ext cx="19879945" cy="8183245"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2269,8 +2688,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18894425" y="0"/>
-          <a:ext cx="16078200" cy="7294245"/>
+          <a:off x="20121245" y="0"/>
+          <a:ext cx="17129760" cy="8162925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2309,8 +2728,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="34730690" y="0"/>
-          <a:ext cx="14796135" cy="2218055"/>
+          <a:off x="37009070" y="0"/>
+          <a:ext cx="15760065" cy="2469515"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2328,7 +2747,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I26" totalsRowShown="0">
-  <autoFilter ref="A1:I26"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I26" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="9">
     <tableColumn id="1" name="N°"/>
     <tableColumn id="2" name="Stage"/>
@@ -2346,7 +2765,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H106" totalsRowShown="0">
-  <autoFilter ref="A1:H106">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H106" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="equal" val="1"/>
@@ -2547,7 +2966,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.68333333333333" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="8" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -2562,19 +2981,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultColWidth="8.68333333333333" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.45" customWidth="1"/>
-    <col min="2" max="2" width="7.81666666666667" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" customWidth="1"/>
+    <col min="2" max="2" width="7.8203125" customWidth="1"/>
     <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="28.8166666666667" customWidth="1"/>
+    <col min="4" max="4" width="32.4140625" customWidth="1"/>
     <col min="5" max="5" width="57" customWidth="1"/>
-    <col min="6" max="6" width="15.5416666666667" customWidth="1"/>
-    <col min="7" max="7" width="8.54166666666667" customWidth="1"/>
-    <col min="8" max="8" width="27.5416666666667" customWidth="1"/>
+    <col min="6" max="6" width="15.5390625" customWidth="1"/>
+    <col min="7" max="7" width="8.5390625" customWidth="1"/>
+    <col min="8" max="8" width="27.5390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="1:9">
+    <row r="1" ht="20.4" spans="1:9">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -2603,7 +3022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="18.75" spans="1:9">
+    <row r="2" ht="20.4" spans="1:9">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2623,10 +3042,10 @@
         <v>12</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="15"/>
+      <c r="H2" s="18"/>
       <c r="I2" s="14"/>
     </row>
-    <row r="3" ht="18.75" spans="1:9">
+    <row r="3" ht="20.4" spans="1:9">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2646,10 +3065,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="6"/>
-      <c r="H3" s="15"/>
+      <c r="H3" s="18"/>
       <c r="I3" s="14"/>
     </row>
-    <row r="4" ht="18.75" spans="1:9">
+    <row r="4" ht="20.4" spans="1:9">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2669,10 +3088,10 @@
         <v>12</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="15"/>
+      <c r="H4" s="18"/>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" ht="60" spans="1:7">
+    <row r="5" ht="68" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2693,7 +3112,7 @@
       </c>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" ht="17" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2714,7 +3133,7 @@
       </c>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" ht="75" spans="1:7">
+    <row r="7" ht="101" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2724,7 +3143,7 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="15" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -2735,7 +3154,7 @@
       </c>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" ht="30" spans="1:7">
+    <row r="8" ht="34" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2748,7 +3167,7 @@
       <c r="D8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F8" t="s">
@@ -2756,7 +3175,7 @@
       </c>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" ht="30" spans="1:7">
+    <row r="9" ht="34" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2767,17 +3186,17 @@
         <v>29</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" ht="30" spans="1:7">
+    <row r="10" ht="34" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2785,20 +3204,20 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>32</v>
+      <c r="E10" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" ht="45" spans="1:7">
+    <row r="11" ht="51" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2806,20 +3225,20 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="16" t="s">
         <v>36</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>37</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" ht="135" spans="1:7">
+    <row r="12" ht="168" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2827,20 +3246,20 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="6" t="s">
         <v>38</v>
       </c>
+      <c r="D12" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" ht="120" spans="1:7">
+    <row r="13" ht="152" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2848,20 +3267,20 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>40</v>
-      </c>
       <c r="G13" s="6"/>
     </row>
-    <row r="14" ht="90" spans="1:7">
+    <row r="14" ht="118" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2869,20 +3288,20 @@
         <v>1</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="E14" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="F14" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" ht="90" spans="1:6">
+    <row r="15" ht="118" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2890,217 +3309,217 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" spans="2:9">
+    </row>
+    <row r="16" ht="20.4" spans="2:9">
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="15"/>
+      <c r="H16" s="18"/>
       <c r="I16" s="14"/>
     </row>
-    <row r="17" ht="18.75" spans="2:9">
+    <row r="17" ht="20.4" spans="2:9">
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="H17" s="15"/>
+      <c r="H17" s="18"/>
       <c r="I17" s="14"/>
     </row>
-    <row r="18" ht="30" spans="2:9">
+    <row r="18" ht="34" spans="2:9">
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="6"/>
-      <c r="H18" s="15"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="14"/>
     </row>
-    <row r="19" ht="120" spans="2:9">
+    <row r="19" ht="135" spans="2:9">
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G19" s="6"/>
-      <c r="H19" s="15"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="14"/>
     </row>
-    <row r="20" ht="18.75" spans="2:9">
+    <row r="20" ht="20.4" spans="2:9">
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="6"/>
-      <c r="H20" s="15"/>
+      <c r="H20" s="18"/>
       <c r="I20" s="14"/>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" ht="17" spans="2:7">
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" ht="105" spans="2:7">
+    <row r="22" ht="118" spans="2:7">
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" ht="90" spans="2:7">
+    <row r="23" ht="101" spans="2:7">
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" ht="120" spans="2:7">
+    <row r="24" ht="135" spans="2:7">
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" ht="150" spans="2:7">
+    <row r="25" ht="168" spans="2:7">
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" ht="90" spans="2:7">
+    <row r="26" ht="118" spans="2:7">
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>49</v>
+        <v>75</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G26" s="6"/>
     </row>
@@ -3120,41 +3539,41 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H106"/>
-  <sheetFormatPr defaultColWidth="8.68333333333333" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="14.2666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.7333333333333" customWidth="1"/>
-    <col min="3" max="3" width="25.5416666666667" customWidth="1"/>
-    <col min="5" max="5" width="44.1833333333333" customWidth="1"/>
+    <col min="1" max="1" width="14.265625" customWidth="1"/>
+    <col min="2" max="2" width="23.734375" customWidth="1"/>
+    <col min="3" max="3" width="33.8828125" customWidth="1"/>
+    <col min="5" max="5" width="44.1796875" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="15.45" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="5" customFormat="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3165,23 +3584,23 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="30" spans="1:8">
+    <row r="3" ht="34" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3189,25 +3608,25 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" t="s">
         <v>89</v>
       </c>
-      <c r="G3" t="s">
-        <v>85</v>
-      </c>
       <c r="H3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" ht="17" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3215,25 +3634,25 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="2:8">
+    <row r="5" ht="17" spans="2:8">
       <c r="B5" t="s">
         <v>10</v>
       </c>
@@ -3241,73 +3660,73 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="30" spans="2:8">
+    <row r="6" ht="34" spans="2:8">
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" ht="17" spans="2:8">
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
         <v>98</v>
       </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="45.75" spans="2:8">
+    <row r="8" ht="51" spans="2:8">
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -3318,13 +3737,13 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -3335,73 +3754,73 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="75" spans="2:8">
+    <row r="11" ht="84" spans="2:8">
       <c r="B11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="30" spans="2:8">
+    <row r="12" ht="34" spans="2:8">
       <c r="B12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" t="s">
         <v>110</v>
       </c>
-      <c r="D12" t="s">
-        <v>106</v>
-      </c>
       <c r="E12" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="60" spans="2:8">
+    <row r="13" ht="68" spans="2:8">
       <c r="B13" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -3412,16 +3831,16 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -3432,439 +3851,439 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="30.75" spans="2:8">
+    <row r="16" ht="34" spans="2:8">
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="30" spans="2:8">
+    <row r="17" ht="34" spans="2:8">
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="150" spans="2:8">
+    <row r="18" ht="168" spans="2:8">
       <c r="B18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="60" spans="2:8">
+    <row r="19" ht="84" spans="2:8">
       <c r="B19" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="84" spans="2:8">
+      <c r="B20" t="s">
         <v>125</v>
       </c>
-      <c r="G19" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="75" spans="2:8">
-      <c r="B20" t="s">
-        <v>121</v>
-      </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="105" spans="2:8">
+    <row r="21" ht="118" spans="2:8">
       <c r="B21" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="105" spans="2:8">
+    <row r="22" ht="118" spans="2:8">
       <c r="B22" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="195" spans="2:8">
+    <row r="23" ht="219" spans="2:8">
       <c r="B23" t="s">
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" ht="17" spans="2:8">
       <c r="B24" t="s">
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="330" spans="2:8">
+    <row r="25" ht="370" spans="2:8">
       <c r="B25" t="s">
         <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="45" spans="2:8">
+    <row r="26" ht="51" spans="2:8">
       <c r="B26" t="s">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="150" spans="2:8">
+    <row r="27" ht="185" spans="2:8">
       <c r="B27" t="s">
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="75" spans="2:8">
+    <row r="28" ht="101" spans="2:8">
       <c r="B28" t="s">
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G28" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="75" spans="2:8">
+    <row r="29" ht="84" spans="2:8">
       <c r="B29" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" ht="17" spans="2:8">
       <c r="B30" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="30" spans="2:8">
+    <row r="31" ht="34" spans="2:8">
       <c r="B31" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G31" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="17" spans="2:8">
+      <c r="B32" t="s">
         <v>153</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" t="s">
-        <v>85</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" t="s">
-        <v>148</v>
-      </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" ht="17" spans="2:8">
       <c r="B33" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G33" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="150" hidden="1" spans="2:5">
+    <row r="34" ht="168" hidden="1" spans="2:5">
       <c r="B34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="35" ht="135" hidden="1" spans="2:5">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" ht="152" hidden="1" spans="2:5">
       <c r="B35" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C35" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="36" ht="135" spans="2:8">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" ht="152" spans="2:8">
       <c r="B36" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F36" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -3872,39 +4291,39 @@
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G37" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" ht="150" spans="2:8">
+    <row r="38" ht="168" spans="2:8">
       <c r="B38" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F38" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G38" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -3912,39 +4331,39 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
+        <v>178</v>
+      </c>
+      <c r="D39" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" t="s">
+        <v>97</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="168" spans="2:8">
+      <c r="B40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40" t="s">
         <v>172</v>
       </c>
-      <c r="D39" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" t="s">
-        <v>93</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" ht="150" spans="2:8">
-      <c r="B40" t="s">
-        <v>164</v>
-      </c>
-      <c r="C40" t="s">
-        <v>173</v>
-      </c>
-      <c r="D40" t="s">
-        <v>166</v>
-      </c>
       <c r="E40" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F40" t="s">
         <v>174</v>
       </c>
-      <c r="F40" t="s">
-        <v>168</v>
-      </c>
       <c r="G40" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -3952,39 +4371,39 @@
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C41" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G41" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="165" spans="2:8">
+    <row r="42" ht="185" spans="2:8">
       <c r="B42" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C42" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F42" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G42" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -3992,39 +4411,39 @@
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G43" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="135" spans="2:8">
+    <row r="44" ht="152" spans="2:8">
       <c r="B44" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D44" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F44" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G44" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -4032,16 +4451,16 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C45" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G45" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -4049,19 +4468,19 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C46" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F46" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -4069,56 +4488,56 @@
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C47" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D47" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G47" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" ht="17" spans="2:8">
       <c r="B48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D48" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G48" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H48">
         <v>2</v>
       </c>
     </row>
-    <row r="49" ht="30" spans="2:8">
+    <row r="49" ht="34" spans="2:8">
       <c r="B49" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D49" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="G49" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -4126,258 +4545,258 @@
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D50" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G50" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H50">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
+    <row r="51" ht="17" spans="2:8">
       <c r="B51" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D51" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F51" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="G51" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H51">
         <v>2</v>
       </c>
     </row>
-    <row r="52" ht="30" spans="2:8">
+    <row r="52" ht="34" spans="2:8">
       <c r="B52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D52" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F52" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="G52" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" ht="30" spans="2:8">
+    <row r="53" ht="34" spans="2:8">
       <c r="B53" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C53" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="G53" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H53">
         <v>2</v>
       </c>
     </row>
-    <row r="54" ht="30" spans="2:8">
+    <row r="54" ht="34" spans="2:8">
       <c r="B54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D54" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G54" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H54">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
+    <row r="55" ht="34" spans="2:8">
       <c r="B55" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D55" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F55" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G55" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H55">
         <v>2</v>
       </c>
     </row>
-    <row r="56" ht="90" spans="2:8">
+    <row r="56" ht="101" spans="2:8">
       <c r="B56" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D56" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G56" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H56">
         <v>2</v>
       </c>
     </row>
-    <row r="57" ht="75" spans="2:8">
+    <row r="57" ht="84" spans="2:8">
       <c r="B57" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D57" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F57" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G57" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H57">
         <v>2</v>
       </c>
     </row>
-    <row r="58" ht="90" spans="2:8">
+    <row r="58" ht="101" spans="2:8">
       <c r="B58" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D58" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G58" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H58">
         <v>2</v>
       </c>
     </row>
-    <row r="59" ht="60" spans="2:8">
+    <row r="59" ht="68" spans="2:8">
       <c r="B59" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D59" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G59" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H59">
         <v>2</v>
       </c>
     </row>
-    <row r="60" ht="30" spans="2:8">
+    <row r="60" ht="51" spans="2:8">
       <c r="B60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C60" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D60" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="G60" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H60">
         <v>2</v>
       </c>
     </row>
-    <row r="61" ht="45" spans="2:8">
+    <row r="61" ht="51" spans="2:8">
       <c r="B61" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C61" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G61" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H61">
         <v>2</v>
@@ -4385,645 +4804,645 @@
     </row>
     <row r="62" ht="409.5" hidden="1" spans="2:7">
       <c r="B62" s="8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G62" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" ht="60" spans="2:8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" ht="68" spans="2:8">
       <c r="B63" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C63" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D63" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H63">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
+    <row r="64" ht="17" spans="2:8">
       <c r="B64" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C64" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="G64" t="s">
+        <v>89</v>
+      </c>
+      <c r="H64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" ht="101" spans="2:8">
+      <c r="B65" t="s">
         <v>228</v>
       </c>
-      <c r="D64" t="s">
-        <v>94</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="G64" t="s">
-        <v>85</v>
-      </c>
-      <c r="H64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" ht="75" spans="2:8">
-      <c r="B65" t="s">
-        <v>222</v>
-      </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D65" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G65" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H65">
         <v>2</v>
       </c>
     </row>
-    <row r="66" ht="30" spans="2:8">
+    <row r="66" ht="51" spans="2:8">
       <c r="B66" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C66" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F66" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G66" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H66">
         <v>2</v>
       </c>
     </row>
-    <row r="67" ht="45" spans="2:8">
+    <row r="67" ht="51" spans="2:8">
       <c r="B67" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C67" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D67" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="G67" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
     </row>
-    <row r="68" ht="30" spans="2:8">
+    <row r="68" ht="34" spans="2:8">
       <c r="B68" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C68" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D68" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G68" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H68">
         <v>2</v>
       </c>
     </row>
-    <row r="69" ht="60" hidden="1" spans="2:8">
+    <row r="69" ht="68" hidden="1" spans="2:8">
       <c r="B69" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D69" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="G69" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H69">
         <v>4</v>
       </c>
     </row>
-    <row r="70" ht="45" hidden="1" spans="2:8">
+    <row r="70" ht="51" hidden="1" spans="2:8">
       <c r="B70" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D70" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G70" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H70">
         <v>4</v>
       </c>
     </row>
-    <row r="71" ht="30" hidden="1" spans="2:8">
+    <row r="71" ht="34" hidden="1" spans="2:8">
       <c r="B71" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D71" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="G71" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H71">
         <v>4</v>
       </c>
     </row>
-    <row r="72" ht="30" hidden="1" spans="2:8">
+    <row r="72" ht="34" hidden="1" spans="2:8">
       <c r="B72" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D72" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G72" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H72">
         <v>4</v>
       </c>
     </row>
-    <row r="73" ht="60" hidden="1" spans="2:8">
+    <row r="73" ht="68" hidden="1" spans="2:8">
       <c r="B73" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D73" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G73" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H73">
         <v>4</v>
       </c>
     </row>
-    <row r="74" ht="30" hidden="1" spans="2:8">
+    <row r="74" ht="34" hidden="1" spans="2:8">
       <c r="B74" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D74" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G74" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H74">
         <v>4</v>
       </c>
     </row>
-    <row r="75" ht="60" hidden="1" spans="2:8">
+    <row r="75" ht="84" hidden="1" spans="2:8">
       <c r="B75" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G75" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H75">
         <v>4</v>
       </c>
     </row>
-    <row r="76" ht="45" hidden="1" spans="2:8">
+    <row r="76" ht="51" hidden="1" spans="2:8">
       <c r="B76" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D76" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F76" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="G76" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H76">
         <v>4</v>
       </c>
     </row>
-    <row r="77" ht="45" spans="2:8">
+    <row r="77" ht="51" spans="2:8">
       <c r="B77" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G77" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H77">
         <v>2</v>
       </c>
     </row>
-    <row r="78" ht="75" spans="2:8">
+    <row r="78" ht="101" spans="2:8">
       <c r="B78" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C78" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D78" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G78" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H78">
         <v>2</v>
       </c>
     </row>
-    <row r="79" ht="75" spans="2:8">
+    <row r="79" ht="84" spans="2:8">
       <c r="B79" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C79" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D79" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G79" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H79">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="2:8">
+    <row r="80" ht="17" spans="2:8">
       <c r="B80" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D80" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E80" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G80" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H80">
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" ht="17" spans="2:8">
       <c r="B81" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D81" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E81" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G81" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H81">
         <v>2</v>
       </c>
     </row>
-    <row r="82" ht="30" spans="2:8">
+    <row r="82" ht="34" spans="2:8">
       <c r="B82" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C82" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D82" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="G82" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H82">
         <v>2</v>
       </c>
     </row>
-    <row r="83" ht="30" spans="2:8">
+    <row r="83" ht="34" spans="2:8">
       <c r="B83" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C83" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D83" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="G83" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H83">
         <v>2</v>
       </c>
     </row>
-    <row r="84" ht="30" spans="2:8">
+    <row r="84" ht="34" spans="2:8">
       <c r="B84" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C84" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D84" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="G84" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H84">
         <v>2</v>
       </c>
     </row>
-    <row r="85" ht="30" spans="2:8">
+    <row r="85" ht="34" spans="2:8">
       <c r="B85" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C85" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D85" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G85" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H85">
         <v>2</v>
       </c>
     </row>
-    <row r="86" ht="45" spans="2:8">
+    <row r="86" ht="51" spans="2:8">
       <c r="B86" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C86" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D86" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="G86" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H86">
         <v>2</v>
       </c>
     </row>
-    <row r="87" ht="45" spans="2:8">
+    <row r="87" ht="51" spans="2:8">
       <c r="B87" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C87" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D87" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G87" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H87">
         <v>2</v>
       </c>
     </row>
-    <row r="88" ht="30" spans="2:8">
+    <row r="88" ht="34" spans="2:8">
       <c r="B88" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C88" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D88" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G88" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H88">
         <v>2</v>
       </c>
     </row>
-    <row r="89" ht="45" hidden="1" spans="2:5">
+    <row r="89" ht="51" hidden="1" spans="2:5">
       <c r="B89" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C89" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D89" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="90" ht="30" spans="2:8">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="90" ht="34" spans="2:8">
       <c r="B90" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C90" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D90" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G90" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H90">
         <v>2</v>
       </c>
     </row>
-    <row r="91" ht="30" spans="2:8">
+    <row r="91" ht="34" spans="2:8">
       <c r="B91" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C91" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D91" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G91" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H91">
         <v>2</v>
       </c>
     </row>
-    <row r="92" ht="30" spans="2:8">
+    <row r="92" ht="34" spans="2:8">
       <c r="B92" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C92" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D92" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G92" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H92">
         <v>2</v>
       </c>
     </row>
-    <row r="93" ht="45" spans="2:8">
+    <row r="93" ht="51" spans="2:8">
       <c r="B93" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C93" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D93" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="G93" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H93">
         <v>2</v>
@@ -5031,80 +5450,80 @@
     </row>
     <row r="94" spans="2:8">
       <c r="B94" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C94" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D94" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E94" s="6"/>
       <c r="G94" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H94">
         <v>2</v>
       </c>
     </row>
-    <row r="95" ht="45" spans="2:8">
+    <row r="95" ht="51" spans="2:8">
       <c r="B95" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C95" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D95" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G95" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H95">
         <v>2</v>
       </c>
     </row>
-    <row r="96" ht="45" spans="2:8">
+    <row r="96" ht="51" spans="2:8">
       <c r="B96" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C96" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D96" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G96" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H96">
         <v>2</v>
       </c>
     </row>
-    <row r="97" ht="317.25" spans="2:8">
+    <row r="97" ht="370" spans="2:8">
       <c r="B97" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C97" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D97" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F97" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G97" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H97">
         <v>2</v>
@@ -5112,39 +5531,39 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C98" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D98" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G98" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H98">
         <v>2</v>
       </c>
     </row>
-    <row r="99" ht="152.25" spans="2:8">
+    <row r="99" ht="185" spans="2:8">
       <c r="B99" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C99" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D99" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F99" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G99" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H99">
         <v>2</v>
@@ -5152,39 +5571,39 @@
     </row>
     <row r="100" spans="2:8">
       <c r="B100" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C100" t="s">
+        <v>309</v>
+      </c>
+      <c r="D100" t="s">
+        <v>98</v>
+      </c>
+      <c r="G100" t="s">
+        <v>97</v>
+      </c>
+      <c r="H100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" ht="202" spans="2:8">
+      <c r="B101" t="s">
         <v>303</v>
       </c>
-      <c r="D100" t="s">
-        <v>94</v>
-      </c>
-      <c r="G100" t="s">
-        <v>93</v>
-      </c>
-      <c r="H100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" ht="182.25" spans="2:8">
-      <c r="B101" t="s">
-        <v>297</v>
-      </c>
       <c r="C101" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D101" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F101" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G101" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H101">
         <v>2</v>
@@ -5192,39 +5611,39 @@
     </row>
     <row r="102" spans="2:8">
       <c r="B102" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C102" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D102" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G102" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H102">
         <v>2</v>
       </c>
     </row>
-    <row r="103" ht="135.75" spans="2:8">
+    <row r="103" ht="152" spans="2:8">
       <c r="B103" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C103" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="D103" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F103" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G103" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H103">
         <v>2</v>
@@ -5232,16 +5651,16 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C104" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D104" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G104" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H104">
         <v>2</v>
@@ -5249,19 +5668,19 @@
     </row>
     <row r="105" spans="2:8">
       <c r="B105" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C105" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D105" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F105" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G105" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H105">
         <v>2</v>
@@ -5269,16 +5688,16 @@
     </row>
     <row r="106" spans="2:8">
       <c r="B106" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C106" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D106" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G106" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H106">
         <v>2</v>
@@ -5300,7 +5719,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.68333333333333" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="8" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -5313,140 +5732,140 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="8.68333333333333" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="26.5416666666667" customWidth="1"/>
-    <col min="2" max="2" width="78.7333333333333" customWidth="1"/>
+    <col min="1" max="1" width="26.5390625" customWidth="1"/>
+    <col min="2" max="2" width="78.734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="2" ht="30" spans="1:2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" ht="34" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="3" ht="30" spans="1:2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" ht="34" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="4" ht="30" spans="1:2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4" ht="34" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="6" ht="30" spans="1:2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="6" ht="34" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B9" s="4"/>
     </row>
-    <row r="10" ht="45" spans="1:2">
+    <row r="10" ht="51" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="12" ht="30" spans="1:2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="12" ht="34" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="13" ht="17" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="1:2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" ht="34" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="1:2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="15" ht="34" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="16" ht="30" spans="1:2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="16" ht="34" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="17" ht="30" spans="1:2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="17" ht="34" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/Data/MAP Stages- Inputs_Outputs.xlsx
+++ b/Data/MAP Stages- Inputs_Outputs.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13840" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="29100" windowHeight="14440" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Process Diagram" sheetId="1" r:id="rId1"/>
     <sheet name=" Process Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Fields" sheetId="3" r:id="rId3"/>
-    <sheet name="Organigram" sheetId="4" r:id="rId4"/>
-    <sheet name="Glossary_Lifecycle" sheetId="5" r:id="rId5"/>
+    <sheet name=" Process Data_Cleaned" sheetId="6" r:id="rId3"/>
+    <sheet name="Fields" sheetId="3" r:id="rId4"/>
+    <sheet name="Organigram" sheetId="4" r:id="rId5"/>
+    <sheet name="Glossary_Lifecycle" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="353">
   <si>
     <t>N°</t>
   </si>
@@ -109,6 +110,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*Mission Statement
 *Business Goals
 *Customer Goals
@@ -187,6 +196,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -234,6 +250,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -254,6 +276,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -290,6 +320,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -371,10 +407,40 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">
-*Project Size 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*Project Size 
 *Impact 
 *Strategic Fit</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>= Project Estimation</t>
+    </r>
   </si>
   <si>
     <t>One Pager Template</t>
@@ -387,6 +453,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*Mission Statement
 *Business Goals
 *Customer Goals
@@ -454,6 +528,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">MAP Project Charter </t>
     </r>
     <r>
@@ -477,6 +557,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">MAP project rating </t>
     </r>
     <r>
@@ -500,6 +586,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">MAP project rating </t>
     </r>
     <r>
@@ -631,6 +723,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">Approval for moving to Stage </t>
     </r>
     <r>
@@ -655,6 +753,134 @@
     </r>
   </si>
   <si>
+    <t>Idea description
+Market review report
+Competitor Analysis report
+Portfolio Review report</t>
+  </si>
+  <si>
+    <t>Project Charter</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>*r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>essources allocation</t>
+    </r>
+  </si>
+  <si>
+    <t>Mision One Pager
+Project Estimation
+*ressources allocation</t>
+  </si>
+  <si>
+    <t>MAP Duration</t>
+  </si>
+  <si>
+    <r>
+      <t>Problem Canvas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mission One Pager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Project Estimation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mission One Pager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Project Charter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+*ressources allocation
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>MAP Duration</t>
+    </r>
+  </si>
+  <si>
+    <t>MAP Project Charter</t>
+  </si>
+  <si>
     <t>Field ID</t>
   </si>
   <si>
@@ -883,9 +1109,6 @@
     <t xml:space="preserve">Explain the impact of the system. Consider its success on the market, if it is a niche market, a door opener to other projects, its estimated revenue for the organization, its influence on the positioning of the brands on the market and its differentiation with competitors. </t>
   </si>
   <si>
-    <t>Project Charter</t>
-  </si>
-  <si>
     <t>List of Major Risks</t>
   </si>
   <si>
@@ -917,9 +1140,6 @@
   </si>
   <si>
     <t xml:space="preserve">assign team members to the listed resources. </t>
-  </si>
-  <si>
-    <t>MAP Duration</t>
   </si>
   <si>
     <t>MAP lead time</t>
@@ -944,9 +1164,6 @@
   </si>
   <si>
     <t>MAP Project Charter Template</t>
-  </si>
-  <si>
-    <t>MAP Project Charter</t>
   </si>
   <si>
     <t>Template reporting the different fields:
@@ -1583,6 +1800,24 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <strike/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1599,23 +1834,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="1"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1778,6 +2001,7 @@
       <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <strike/>
@@ -1790,13 +2014,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <charset val="1"/>
       <scheme val="minor"/>
@@ -2164,21 +2381,18 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2187,119 +2401,122 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2328,17 +2545,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2764,6 +2985,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1_4" displayName="Table1_4" ref="A1:I26" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I26" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="N°"/>
+    <tableColumn id="2" name="Stage"/>
+    <tableColumn id="3" name="Step"/>
+    <tableColumn id="4" name="Input fields or cluster"/>
+    <tableColumn id="5" name="Output fields or cluster"/>
+    <tableColumn id="6" name="R"/>
+    <tableColumn id="7" name="A"/>
+    <tableColumn id="8" name="C"/>
+    <tableColumn id="9" name="I"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H106" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H106" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="7">
@@ -3042,7 +3281,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="18"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="14"/>
     </row>
     <row r="3" ht="20.4" spans="1:9">
@@ -3065,7 +3304,7 @@
         <v>12</v>
       </c>
       <c r="G3" s="6"/>
-      <c r="H3" s="18"/>
+      <c r="H3" s="17"/>
       <c r="I3" s="14"/>
     </row>
     <row r="4" ht="20.4" spans="1:9">
@@ -3088,7 +3327,7 @@
         <v>12</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="18"/>
+      <c r="H4" s="17"/>
       <c r="I4" s="14"/>
     </row>
     <row r="5" ht="68" spans="1:7">
@@ -3143,7 +3382,7 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="20" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -3167,7 +3406,7 @@
       <c r="D8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="22" t="s">
         <v>28</v>
       </c>
       <c r="F8" t="s">
@@ -3209,7 +3448,7 @@
       <c r="D10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>33</v>
       </c>
       <c r="F10" t="s">
@@ -3227,10 +3466,10 @@
       <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
         <v>37</v>
       </c>
       <c r="F11" t="s">
@@ -3238,7 +3477,7 @@
       </c>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" ht="168" spans="1:7">
+    <row r="12" ht="185" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3248,7 +3487,7 @@
       <c r="C12" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E12" t="s">
@@ -3269,10 +3508,10 @@
       <c r="C13" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>44</v>
       </c>
       <c r="F13" t="s">
@@ -3293,7 +3532,7 @@
       <c r="D14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -3311,7 +3550,7 @@
       <c r="C15" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -3338,7 +3577,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" ht="20.4" spans="2:9">
@@ -3355,7 +3594,7 @@
         <v>55</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" ht="34" spans="2:9">
@@ -3375,7 +3614,7 @@
         <v>12</v>
       </c>
       <c r="G18" s="6"/>
-      <c r="H18" s="18"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="14"/>
     </row>
     <row r="19" ht="135" spans="2:9">
@@ -3392,7 +3631,7 @@
         <v>60</v>
       </c>
       <c r="G19" s="6"/>
-      <c r="H19" s="18"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" ht="20.4" spans="2:9">
@@ -3412,7 +3651,7 @@
         <v>12</v>
       </c>
       <c r="G20" s="6"/>
-      <c r="H20" s="18"/>
+      <c r="H20" s="17"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" ht="17" spans="2:7">
@@ -3515,7 +3754,7 @@
       <c r="D26" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="16" t="s">
         <v>77</v>
       </c>
       <c r="F26" s="6" t="s">
@@ -3534,6 +3773,564 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="5.453125" customWidth="1"/>
+    <col min="2" max="2" width="7.8203125" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="32.4140625" customWidth="1"/>
+    <col min="5" max="5" width="57" customWidth="1"/>
+    <col min="6" max="6" width="15.5390625" customWidth="1"/>
+    <col min="7" max="7" width="8.5390625" customWidth="1"/>
+    <col min="8" max="8" width="27.5390625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.4" spans="1:9">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="20.4" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="14"/>
+    </row>
+    <row r="3" ht="20.4" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" ht="20.4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="14"/>
+    </row>
+    <row r="5" ht="68" spans="1:7">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" ht="17" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" ht="17" spans="1:7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" ht="34" spans="1:7">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" ht="34" spans="1:7">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" ht="34" spans="1:7">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" ht="51" spans="1:7">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" ht="51" spans="1:7">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" ht="68" spans="1:7">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" ht="118" spans="1:7">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" ht="118" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" ht="20.4" spans="2:9">
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" ht="20.4" spans="2:9">
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" ht="34" spans="2:9">
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" ht="135" spans="2:9">
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" ht="20.4" spans="2:9">
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="21" ht="17" spans="2:7">
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" ht="118" spans="2:7">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" ht="101" spans="2:7">
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" ht="135" spans="2:7">
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" ht="168" spans="2:7">
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" ht="118" spans="2:7">
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="8" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3552,28 +4349,28 @@
   <sheetData>
     <row r="1" s="5" customFormat="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3584,17 +4381,17 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -3608,19 +4405,19 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -3634,19 +4431,19 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -3660,13 +4457,13 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -3677,16 +4474,16 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -3697,16 +4494,16 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -3717,16 +4514,16 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -3737,13 +4534,13 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -3754,13 +4551,13 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -3768,19 +4565,19 @@
     </row>
     <row r="11" ht="84" spans="2:8">
       <c r="B11" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G11" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -3788,19 +4585,19 @@
     </row>
     <row r="12" ht="34" spans="2:8">
       <c r="B12" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -3808,19 +4605,19 @@
     </row>
     <row r="13" ht="68" spans="2:8">
       <c r="B13" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -3831,16 +4628,16 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G14" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -3851,16 +4648,16 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -3871,16 +4668,16 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -3891,16 +4688,16 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -3908,19 +4705,19 @@
     </row>
     <row r="18" ht="168" spans="2:8">
       <c r="B18" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G18" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -3928,19 +4725,19 @@
     </row>
     <row r="19" ht="84" spans="2:8">
       <c r="B19" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -3948,19 +4745,19 @@
     </row>
     <row r="20" ht="84" spans="2:8">
       <c r="B20" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G20" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -3968,19 +4765,19 @@
     </row>
     <row r="21" ht="118" spans="2:8">
       <c r="B21" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G21" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -3988,19 +4785,19 @@
     </row>
     <row r="22" ht="118" spans="2:8">
       <c r="B22" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -4011,19 +4808,19 @@
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F23" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -4034,16 +4831,16 @@
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -4054,19 +4851,19 @@
         <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F25" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -4077,16 +4874,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G26" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -4097,19 +4894,19 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F27" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G27" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -4120,16 +4917,16 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G28" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -4137,19 +4934,19 @@
     </row>
     <row r="29" ht="84" spans="2:8">
       <c r="B29" t="s">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G29" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -4157,22 +4954,22 @@
     </row>
     <row r="30" ht="17" spans="2:8">
       <c r="B30" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F30" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G30" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -4180,19 +4977,19 @@
     </row>
     <row r="31" ht="34" spans="2:8">
       <c r="B31" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G31" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -4200,19 +4997,19 @@
     </row>
     <row r="32" ht="17" spans="2:8">
       <c r="B32" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -4220,19 +5017,19 @@
     </row>
     <row r="33" ht="17" spans="2:8">
       <c r="B33" t="s">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -4246,44 +5043,44 @@
         <v>40</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" ht="152" hidden="1" spans="2:5">
       <c r="B35" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" ht="152" spans="2:8">
       <c r="B36" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F36" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -4291,16 +5088,16 @@
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G37" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -4308,22 +5105,22 @@
     </row>
     <row r="38" ht="168" spans="2:8">
       <c r="B38" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C38" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F38" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G38" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -4331,16 +5128,16 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C39" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G39" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -4348,22 +5145,22 @@
     </row>
     <row r="40" ht="168" spans="2:8">
       <c r="B40" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C40" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F40" t="s">
         <v>179</v>
       </c>
-      <c r="D40" t="s">
-        <v>172</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F40" t="s">
-        <v>174</v>
-      </c>
       <c r="G40" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -4371,16 +5168,16 @@
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C41" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G41" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -4388,22 +5185,22 @@
     </row>
     <row r="42" ht="185" spans="2:8">
       <c r="B42" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C42" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F42" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G42" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -4411,16 +5208,16 @@
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C43" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G43" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -4428,22 +5225,22 @@
     </row>
     <row r="44" ht="152" spans="2:8">
       <c r="B44" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C44" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F44" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G44" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -4451,16 +5248,16 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G45" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -4468,19 +5265,19 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F46" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G46" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -4488,16 +5285,16 @@
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D47" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G47" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -4508,16 +5305,16 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G48" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H48">
         <v>2</v>
@@ -4528,16 +5325,16 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G49" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -4548,17 +5345,17 @@
         <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G50" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -4569,19 +5366,19 @@
         <v>53</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D51" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F51" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G51" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -4592,19 +5389,19 @@
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D52" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F52" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G52" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H52">
         <v>2</v>
@@ -4615,16 +5412,16 @@
         <v>55</v>
       </c>
       <c r="C53" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G53" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -4635,16 +5432,16 @@
         <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G54" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H54">
         <v>2</v>
@@ -4655,19 +5452,19 @@
         <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D55" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F55" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G55" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H55">
         <v>2</v>
@@ -4678,19 +5475,19 @@
         <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D56" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F56" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G56" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H56">
         <v>2</v>
@@ -4701,19 +5498,19 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F57" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G57" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H57">
         <v>2</v>
@@ -4724,19 +5521,19 @@
         <v>55</v>
       </c>
       <c r="C58" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G58" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H58">
         <v>2</v>
@@ -4747,16 +5544,16 @@
         <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D59" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="G59" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H59">
         <v>2</v>
@@ -4767,16 +5564,16 @@
         <v>55</v>
       </c>
       <c r="C60" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D60" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G60" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -4784,19 +5581,19 @@
     </row>
     <row r="61" ht="51" spans="2:8">
       <c r="B61" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C61" t="s">
         <v>58</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G61" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H61">
         <v>2</v>
@@ -4804,39 +5601,39 @@
     </row>
     <row r="62" ht="409.5" hidden="1" spans="2:7">
       <c r="B62" s="8" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G62" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" ht="68" spans="2:8">
       <c r="B63" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C63" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D63" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G63" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H63">
         <v>2</v>
@@ -4844,19 +5641,19 @@
     </row>
     <row r="64" ht="17" spans="2:8">
       <c r="B64" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C64" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D64" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G64" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H64">
         <v>2</v>
@@ -4864,19 +5661,19 @@
     </row>
     <row r="65" ht="101" spans="2:8">
       <c r="B65" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C65" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D65" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G65" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H65">
         <v>2</v>
@@ -4884,22 +5681,22 @@
     </row>
     <row r="66" ht="51" spans="2:8">
       <c r="B66" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C66" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F66" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G66" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H66">
         <v>2</v>
@@ -4907,19 +5704,19 @@
     </row>
     <row r="67" ht="51" spans="2:8">
       <c r="B67" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C67" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G67" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H67">
         <v>2</v>
@@ -4927,19 +5724,19 @@
     </row>
     <row r="68" ht="34" spans="2:8">
       <c r="B68" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C68" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D68" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G68" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H68">
         <v>2</v>
@@ -4947,22 +5744,22 @@
     </row>
     <row r="69" ht="68" hidden="1" spans="2:8">
       <c r="B69" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G69" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H69">
         <v>4</v>
@@ -4970,19 +5767,19 @@
     </row>
     <row r="70" ht="51" hidden="1" spans="2:8">
       <c r="B70" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D70" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G70" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H70">
         <v>4</v>
@@ -4990,22 +5787,22 @@
     </row>
     <row r="71" ht="34" hidden="1" spans="2:8">
       <c r="B71" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D71" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G71" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H71">
         <v>4</v>
@@ -5013,19 +5810,19 @@
     </row>
     <row r="72" ht="34" hidden="1" spans="2:8">
       <c r="B72" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D72" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G72" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H72">
         <v>4</v>
@@ -5033,19 +5830,19 @@
     </row>
     <row r="73" ht="68" hidden="1" spans="2:8">
       <c r="B73" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D73" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="G73" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H73">
         <v>4</v>
@@ -5053,19 +5850,19 @@
     </row>
     <row r="74" ht="34" hidden="1" spans="2:8">
       <c r="B74" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G74" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H74">
         <v>4</v>
@@ -5073,19 +5870,19 @@
     </row>
     <row r="75" ht="84" hidden="1" spans="2:8">
       <c r="B75" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D75" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G75" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H75">
         <v>4</v>
@@ -5093,22 +5890,22 @@
     </row>
     <row r="76" ht="51" hidden="1" spans="2:8">
       <c r="B76" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D76" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F76" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G76" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H76">
         <v>4</v>
@@ -5116,19 +5913,19 @@
     </row>
     <row r="77" ht="51" spans="2:8">
       <c r="B77" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D77" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G77" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H77">
         <v>2</v>
@@ -5136,19 +5933,19 @@
     </row>
     <row r="78" ht="101" spans="2:8">
       <c r="B78" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C78" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D78" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G78" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H78">
         <v>2</v>
@@ -5156,19 +5953,19 @@
     </row>
     <row r="79" ht="84" spans="2:8">
       <c r="B79" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C79" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D79" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G79" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H79">
         <v>2</v>
@@ -5176,19 +5973,19 @@
     </row>
     <row r="80" ht="17" spans="2:8">
       <c r="B80" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D80" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E80" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G80" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H80">
         <v>2</v>
@@ -5196,19 +5993,19 @@
     </row>
     <row r="81" ht="17" spans="2:8">
       <c r="B81" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D81" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E81" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G81" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H81">
         <v>2</v>
@@ -5219,16 +6016,16 @@
         <v>62</v>
       </c>
       <c r="C82" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D82" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G82" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H82">
         <v>2</v>
@@ -5239,16 +6036,16 @@
         <v>62</v>
       </c>
       <c r="C83" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D83" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G83" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H83">
         <v>2</v>
@@ -5259,16 +6056,16 @@
         <v>62</v>
       </c>
       <c r="C84" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D84" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G84" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H84">
         <v>2</v>
@@ -5279,16 +6076,16 @@
         <v>62</v>
       </c>
       <c r="C85" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D85" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G85" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H85">
         <v>2</v>
@@ -5299,16 +6096,16 @@
         <v>62</v>
       </c>
       <c r="C86" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D86" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G86" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H86">
         <v>2</v>
@@ -5319,16 +6116,16 @@
         <v>62</v>
       </c>
       <c r="C87" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D87" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G87" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H87">
         <v>2</v>
@@ -5339,16 +6136,16 @@
         <v>62</v>
       </c>
       <c r="C88" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D88" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G88" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H88">
         <v>2</v>
@@ -5359,13 +6156,13 @@
         <v>62</v>
       </c>
       <c r="C89" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D89" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="90" ht="34" spans="2:8">
@@ -5373,16 +6170,16 @@
         <v>62</v>
       </c>
       <c r="C90" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D90" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G90" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H90">
         <v>2</v>
@@ -5393,16 +6190,16 @@
         <v>62</v>
       </c>
       <c r="C91" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D91" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G91" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -5413,16 +6210,16 @@
         <v>62</v>
       </c>
       <c r="C92" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D92" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G92" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H92">
         <v>2</v>
@@ -5433,16 +6230,16 @@
         <v>62</v>
       </c>
       <c r="C93" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D93" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="G93" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H93">
         <v>2</v>
@@ -5453,14 +6250,14 @@
         <v>62</v>
       </c>
       <c r="C94" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D94" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E94" s="6"/>
       <c r="G94" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H94">
         <v>2</v>
@@ -5471,16 +6268,16 @@
         <v>62</v>
       </c>
       <c r="C95" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D95" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="G95" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -5488,19 +6285,19 @@
     </row>
     <row r="96" ht="51" spans="2:8">
       <c r="B96" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C96" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="G96" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H96">
         <v>2</v>
@@ -5508,22 +6305,22 @@
     </row>
     <row r="97" ht="370" spans="2:8">
       <c r="B97" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C97" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D97" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F97" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G97" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H97">
         <v>2</v>
@@ -5531,16 +6328,16 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C98" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D98" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G98" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H98">
         <v>2</v>
@@ -5548,22 +6345,22 @@
     </row>
     <row r="99" ht="185" spans="2:8">
       <c r="B99" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C99" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D99" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F99" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G99" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H99">
         <v>2</v>
@@ -5571,16 +6368,16 @@
     </row>
     <row r="100" spans="2:8">
       <c r="B100" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C100" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D100" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G100" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H100">
         <v>2</v>
@@ -5588,22 +6385,22 @@
     </row>
     <row r="101" ht="202" spans="2:8">
       <c r="B101" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C101" t="s">
         <v>62</v>
       </c>
       <c r="D101" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F101" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H101">
         <v>2</v>
@@ -5611,16 +6408,16 @@
     </row>
     <row r="102" spans="2:8">
       <c r="B102" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C102" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D102" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G102" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H102">
         <v>2</v>
@@ -5628,22 +6425,22 @@
     </row>
     <row r="103" ht="152" spans="2:8">
       <c r="B103" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C103" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D103" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F103" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G103" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H103">
         <v>2</v>
@@ -5651,16 +6448,16 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C104" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D104" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G104" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H104">
         <v>2</v>
@@ -5668,19 +6465,19 @@
     </row>
     <row r="105" spans="2:8">
       <c r="B105" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C105" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D105" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F105" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G105" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H105">
         <v>2</v>
@@ -5688,16 +6485,16 @@
     </row>
     <row r="106" spans="2:8">
       <c r="B106" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C106" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D106" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G106" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H106">
         <v>2</v>
@@ -5713,7 +6510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5728,7 +6525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B17"/>
@@ -5740,132 +6537,132 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" ht="51" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" ht="34" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" ht="34" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" ht="34" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" ht="34" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" ht="34" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
